--- a/laporan_padel_dki_jakarta_2026-10-09.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-09.xlsx
@@ -8467,16 +8467,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.089.000</t>
+          <t>Rp1.188.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp7.580.000</t>
+          <t>Rp7.830.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-09.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-09.xlsx
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp810.000</t>
+          <t>Rp898.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>68</v>
       </c>
       <c r="D10" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.656.986</t>
+          <t>Rp6.825.986</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp2.664.000</t>
+          <t>Rp3.540.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>127</v>
       </c>
       <c r="D21" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp17.605.000</t>
+          <t>Rp18.005.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp4.650.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp2.625.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.575.000</t>
+          <t>Rp1.475.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1319,16 +1319,16 @@
         <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp564.000</t>
+          <t>Rp689.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp99.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>198</v>
       </c>
       <c r="D44" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>32</v>
       </c>
       <c r="D58" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp1.550.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>36</v>
       </c>
       <c r="D59" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp695.000</t>
+          <t>Rp1.291.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>80</v>
       </c>
       <c r="D60" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp1.195.000</t>
+          <t>Rp995.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>90</v>
       </c>
       <c r="D61" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp5.720.000</t>
+          <t>Rp6.320.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp3.400.000</t>
+          <t>Rp3.475.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>90</v>
       </c>
       <c r="D80" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp4.763.000</t>
+          <t>Rp5.161.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>90</v>
       </c>
       <c r="D89" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp3.240.000</t>
+          <t>Rp3.420.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>64</v>
       </c>
       <c r="D95" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp2.790.000</t>
+          <t>Rp3.040.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>112</v>
       </c>
       <c r="D96" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp3.025.000</t>
+          <t>Rp3.265.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3458,16 +3458,16 @@
         <v>28</v>
       </c>
       <c r="D98" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rp1.295.000</t>
+          <t>Rp1.460.000</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.348.000</t>
+          <t>Rp3.173.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp4.650.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4098,16 +4098,16 @@
         <v>18</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp621.000</t>
+          <t>Rp819.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -4687,16 +4687,16 @@
         <v>32</v>
       </c>
       <c r="D39" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp3.900.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4811,16 +4811,16 @@
         <v>77</v>
       </c>
       <c r="D43" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp11.200.000</t>
+          <t>Rp12.500.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4842,16 +4842,16 @@
         <v>54</v>
       </c>
       <c r="D44" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp500.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4966,16 +4966,16 @@
         <v>80</v>
       </c>
       <c r="D48" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp4.925.000</t>
+          <t>Rp5.425.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>54</v>
       </c>
       <c r="D51" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp7.600.000</t>
+          <t>Rp7.300.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>72</v>
       </c>
       <c r="D53" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp400.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>36</v>
       </c>
       <c r="D61" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp2.380.000</t>
+          <t>Rp2.940.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>90</v>
       </c>
       <c r="D64" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp11.350.000</t>
+          <t>Rp10.850.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.020.000</t>
+          <t>Rp1.280.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.770.000</t>
+          <t>Rp2.140.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>272</v>
       </c>
       <c r="D8" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp29.550.000</t>
+          <t>Rp29.800.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp7.705.000</t>
+          <t>Rp8.040.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.260.000</t>
+          <t>Rp1.440.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp11.810.000</t>
+          <t>Rp12.060.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>79</v>
       </c>
       <c r="D4" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp10.590.000</t>
+          <t>Rp10.815.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>90</v>
       </c>
       <c r="D9" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp8.366.000</t>
+          <t>Rp8.616.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp17.059.000</t>
+          <t>Rp17.229.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp14.660.000</t>
+          <t>Rp15.685.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6844,7 +6844,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp6.025.000</t>
+          <t>Rp5.875.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>60</v>
       </c>
       <c r="D20" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.683.000</t>
+          <t>Rp1.782.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.657.000</t>
+          <t>Rp5.036.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>108</v>
       </c>
       <c r="D33" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp8.750.000</t>
+          <t>Rp10.315.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp12.825.000</t>
+          <t>Rp12.875.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>150</v>
       </c>
       <c r="D40" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp28.610.000</t>
+          <t>Rp29.035.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>174</v>
       </c>
       <c r="D45" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp30.400.000</t>
+          <t>Rp31.000.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>144</v>
       </c>
       <c r="D50" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp5.850.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8095,16 +8095,16 @@
         <v>86</v>
       </c>
       <c r="D5" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp3.800.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.490.000</t>
+          <t>Rp1.640.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp3.705.000</t>
+          <t>Rp4.110.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp950.000</t>
+          <t>Rp1.050.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.125.000</t>
+          <t>Rp2.475.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp15.340.000</t>
+          <t>Rp16.240.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp5.145.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp3.349.992</t>
+          <t>Rp3.724.992</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp3.100.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D33" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp2.347.000</t>
+          <t>Rp2.847.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>128</v>
       </c>
       <c r="D37" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp5.054.000</t>
+          <t>Rp5.252.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-09.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-09.xlsx
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp3.189.000</t>
+          <t>Rp3.387.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp898.000</t>
+          <t>Rp1.074.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp13.101.000</t>
+          <t>Rp13.926.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp4.285.000</t>
+          <t>Rp4.460.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.250.000</t>
+          <t>Rp3.650.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.625.000</t>
+          <t>Rp2.875.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp99.000</t>
+          <t>Rp1.089.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.075.000</t>
+          <t>Rp2.465.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp4.790.000</t>
+          <t>Rp5.188.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>45</v>
       </c>
       <c r="D46" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp300.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1939,16 +1939,16 @@
         <v>28</v>
       </c>
       <c r="D49" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp770.000</t>
+          <t>Rp1.080.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>64</v>
       </c>
       <c r="D51" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp3.168.000</t>
+          <t>Rp3.744.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>32</v>
       </c>
       <c r="D58" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp3.100.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>90</v>
       </c>
       <c r="D61" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp6.320.000</t>
+          <t>Rp6.420.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>34</v>
       </c>
       <c r="D68" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp1.881.000</t>
+          <t>Rp1.980.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>90</v>
       </c>
       <c r="D73" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp2.275.000</t>
+          <t>Rp3.450.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>98</v>
       </c>
       <c r="D75" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp4.010.000</t>
+          <t>Rp4.310.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>114</v>
       </c>
       <c r="D79" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp3.350.000</t>
+          <t>Rp1.850.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>54</v>
       </c>
       <c r="D81" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp1.289.000</t>
+          <t>Rp1.985.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>138</v>
       </c>
       <c r="D88" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp5.550.000</t>
+          <t>Rp5.650.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>112</v>
       </c>
       <c r="D96" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp3.265.000</t>
+          <t>Rp3.585.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp6.865.000</t>
+          <t>Rp7.015.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3757,16 +3757,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.855.000</t>
+          <t>Rp4.230.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3850,16 +3850,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp4.605.000</t>
+          <t>Rp5.395.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.190.000</t>
+          <t>Rp4.925.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.173.000</t>
+          <t>Rp3.348.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.650.000</t>
+          <t>Rp4.950.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.890.000</t>
+          <t>Rp3.060.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>32</v>
       </c>
       <c r="D32" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4501,16 +4501,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp5.475.000</t>
+          <t>Rp5.700.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4563,16 +4563,16 @@
         <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.270.000</t>
+          <t>Rp3.660.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4625,16 +4625,16 @@
         <v>159</v>
       </c>
       <c r="D37" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp25.100.000</t>
+          <t>Rp25.250.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>52</v>
       </c>
       <c r="D41" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4966,16 +4966,16 @@
         <v>80</v>
       </c>
       <c r="D48" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp5.425.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>72</v>
       </c>
       <c r="D50" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp7.344.000</t>
+          <t>Rp7.944.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>162</v>
       </c>
       <c r="D70" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp5.800.000</t>
+          <t>Rp6.900.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.030.000</t>
+          <t>Rp5.390.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.095.000</t>
+          <t>Rp3.525.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp6.325.000</t>
+          <t>Rp6.600.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6257,16 +6257,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.350.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp12.060.000</t>
+          <t>Rp12.340.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp10.815.000</t>
+          <t>Rp10.865.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp8.150.000</t>
+          <t>Rp8.675.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp17.229.000</t>
+          <t>Rp17.059.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.875.000</t>
+          <t>Rp5.275.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.450.000</t>
+          <t>Rp450.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp21.300.000</t>
+          <t>Rp22.500.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.036.000</t>
+          <t>Rp5.117.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>96</v>
       </c>
       <c r="D30" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp5.045.000</t>
+          <t>Rp5.122.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>72</v>
       </c>
       <c r="D32" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.605.000</t>
+          <t>Rp3.955.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp10.315.000</t>
+          <t>Rp10.265.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp12.875.000</t>
+          <t>Rp13.300.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>34</v>
       </c>
       <c r="D38" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp2.304.000</t>
+          <t>Rp2.592.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>150</v>
       </c>
       <c r="D40" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp29.035.000</t>
+          <t>Rp29.460.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>80</v>
       </c>
       <c r="D42" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp3.550.000</t>
+          <t>Rp2.950.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>174</v>
       </c>
       <c r="D45" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp31.000.000</t>
+          <t>Rp31.700.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>76</v>
       </c>
       <c r="D2" t="n">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.915.000</t>
+          <t>Rp2.655.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8064,16 +8064,16 @@
         <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.980.000</t>
+          <t>Rp2.240.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.475.000</t>
+          <t>Rp2.825.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.450.000</t>
+          <t>Rp3.020.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp16.240.000</t>
+          <t>Rp17.680.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp5.290.000</t>
+          <t>Rp5.575.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>32</v>
       </c>
       <c r="D29" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.535.000</t>
+          <t>Rp1.245.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D33" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp2.847.000</t>
+          <t>Rp3.097.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>36</v>
       </c>
       <c r="D36" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.275.000</t>
+          <t>Rp3.510.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>72</v>
       </c>
       <c r="D39" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp3.320.000</t>
+          <t>Rp3.620.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp5.255.000</t>
+          <t>Rp5.555.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -9242,16 +9242,16 @@
         <v>72</v>
       </c>
       <c r="D42" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.475.000</t>
+          <t>Rp2.975.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -9304,16 +9304,16 @@
         <v>64</v>
       </c>
       <c r="D44" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-09.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-09.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp2.140.000</t>
+          <t>Rp2.240.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp3.387.000</t>
+          <t>Rp3.687.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.074.000</t>
+          <t>Rp1.344.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp5.600.000</t>
+          <t>Rp7.040.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>68</v>
       </c>
       <c r="D10" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.825.986</t>
+          <t>Rp7.692.984</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp7.430.000</t>
+          <t>Rp7.930.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.900.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp13.926.000</t>
+          <t>Rp14.201.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -885,16 +885,16 @@
         <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp350.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp1.120.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -947,16 +947,16 @@
         <v>85</v>
       </c>
       <c r="D17" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp3.540.000</t>
+          <t>Rp4.140.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp4.460.000</t>
+          <t>Rp4.670.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.875.000</t>
+          <t>Rp2.625.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.475.000</t>
+          <t>Rp550.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1319,16 +1319,16 @@
         <v>16</v>
       </c>
       <c r="D29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp689.000</t>
+          <t>Rp877.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp2.880.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.089.000</t>
+          <t>Rp1.188.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp5.485.000</t>
+          <t>Rp4.980.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp7.920.000</t>
+          <t>Rp8.420.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.465.000</t>
+          <t>Rp3.245.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>198</v>
       </c>
       <c r="D44" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>60</v>
       </c>
       <c r="D45" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp2.385.000</t>
+          <t>Rp3.645.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1877,16 +1877,16 @@
         <v>54</v>
       </c>
       <c r="D47" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp2.320.000</t>
+          <t>Rp1.220.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -1908,16 +1908,16 @@
         <v>105</v>
       </c>
       <c r="D48" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp5.250.000</t>
+          <t>Rp6.450.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -1939,16 +1939,16 @@
         <v>28</v>
       </c>
       <c r="D49" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp1.080.000</t>
+          <t>Rp1.235.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>64</v>
       </c>
       <c r="D51" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp3.744.000</t>
+          <t>Rp4.320.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>80</v>
       </c>
       <c r="D60" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp995.000</t>
+          <t>Rp1.393.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>68</v>
       </c>
       <c r="D62" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp2.530.000</t>
+          <t>Rp2.880.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>30</v>
       </c>
       <c r="D63" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp236.000</t>
+          <t>Rp295.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>176</v>
       </c>
       <c r="D69" t="n">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp2.988.000</t>
+          <t>Rp4.184.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>108</v>
       </c>
       <c r="D70" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp6.875.000</t>
+          <t>Rp4.825.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>68</v>
       </c>
       <c r="D71" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp2.940.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>72</v>
       </c>
       <c r="D72" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp1.960.000</t>
+          <t>Rp2.185.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>120</v>
       </c>
       <c r="D77" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp6.045.000</t>
+          <t>Rp5.850.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp3.475.000</t>
+          <t>Rp3.775.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2993,16 +2993,16 @@
         <v>14</v>
       </c>
       <c r="D83" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>64</v>
       </c>
       <c r="D95" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp3.040.000</t>
+          <t>Rp3.480.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>112</v>
       </c>
       <c r="D96" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp3.585.000</t>
+          <t>Rp4.485.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3540,16 +3540,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.134.000</t>
+          <t>Rp1.296.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp3.734.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3850,16 +3850,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp5.395.000</t>
+          <t>Rp6.580.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.348.000</t>
+          <t>Rp3.698.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>48</v>
       </c>
       <c r="D15" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.280.000</t>
+          <t>Rp4.840.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp13.400.000</t>
+          <t>Rp13.850.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>65</v>
       </c>
       <c r="D17" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp4.545.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.950.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.060.000</t>
+          <t>Rp3.255.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4315,16 +4315,16 @@
         <v>64</v>
       </c>
       <c r="D27" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp6.625.000</t>
+          <t>Rp7.821.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>180</v>
       </c>
       <c r="D28" t="n">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp18.820.000</t>
+          <t>Rp20.245.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4408,16 +4408,16 @@
         <v>32</v>
       </c>
       <c r="D30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>32</v>
       </c>
       <c r="D32" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4563,16 +4563,16 @@
         <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.660.000</t>
+          <t>Rp3.910.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4687,16 +4687,16 @@
         <v>32</v>
       </c>
       <c r="D39" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp3.900.000</t>
+          <t>Rp3.100.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4966,16 +4966,16 @@
         <v>80</v>
       </c>
       <c r="D48" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp6.000.000</t>
+          <t>Rp6.350.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>90</v>
       </c>
       <c r="D49" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp3.850.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>72</v>
       </c>
       <c r="D50" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp7.944.000</t>
+          <t>Rp8.736.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>54</v>
       </c>
       <c r="D51" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp7.300.000</t>
+          <t>Rp7.600.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>68</v>
       </c>
       <c r="D54" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp10.675.000</t>
+          <t>Rp11.225.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5214,16 +5214,16 @@
         <v>75</v>
       </c>
       <c r="D56" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp142.000</t>
+          <t>Rp275.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5338,16 +5338,16 @@
         <v>45</v>
       </c>
       <c r="D60" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp3.825.000</t>
+          <t>Rp4.300.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5431,16 +5431,16 @@
         <v>34</v>
       </c>
       <c r="D63" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp390.000</t>
+          <t>Rp1.090.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>90</v>
       </c>
       <c r="D64" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp10.850.000</t>
+          <t>Rp11.500.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>30</v>
       </c>
       <c r="D68" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp2.725.000</t>
+          <t>Rp2.875.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5679,16 +5679,16 @@
         <v>90</v>
       </c>
       <c r="D71" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp3.500.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -5792,16 +5792,16 @@
         <v>333</v>
       </c>
       <c r="D3" t="n">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp10.505.000</t>
+          <t>Rp11.385.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5823,16 +5823,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.375.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>108</v>
       </c>
       <c r="D5" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp9.950.000</t>
+          <t>Rp10.550.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.280.000</t>
+          <t>Rp1.940.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>272</v>
       </c>
       <c r="D8" t="n">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp29.800.000</t>
+          <t>Rp32.000.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.390.000</t>
+          <t>Rp5.690.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp2.798.000</t>
+          <t>Rp3.242.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.525.000</t>
+          <t>Rp4.095.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp12.340.000</t>
+          <t>Rp11.140.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>96</v>
       </c>
       <c r="D3" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp8.500.000</t>
+          <t>Rp8.000.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>79</v>
       </c>
       <c r="D4" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp10.865.000</t>
+          <t>Rp11.265.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp138.000</t>
+          <t>Rp337.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>90</v>
       </c>
       <c r="D9" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp8.616.000</t>
+          <t>Rp9.324.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp17.059.000</t>
+          <t>Rp17.789.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp2.900.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp15.685.000</t>
+          <t>Rp15.960.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>102</v>
       </c>
       <c r="D15" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp5.275.000</t>
+          <t>Rp6.775.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp4.084.000</t>
+          <t>Rp4.176.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>60</v>
       </c>
       <c r="D20" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.782.000</t>
+          <t>Rp1.881.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.117.000</t>
+          <t>Rp4.519.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>108</v>
       </c>
       <c r="D25" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp5.200.000</t>
+          <t>Rp6.380.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>68</v>
       </c>
       <c r="D28" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp1.375.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>96</v>
       </c>
       <c r="D30" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp5.122.000</t>
+          <t>Rp5.221.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>96</v>
       </c>
       <c r="D31" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp4.625.000</t>
+          <t>Rp3.925.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>108</v>
       </c>
       <c r="D33" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp10.265.000</t>
+          <t>Rp10.020.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp13.300.000</t>
+          <t>Rp14.150.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>84</v>
       </c>
       <c r="D36" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.425.000</t>
+          <t>Rp1.624.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>170</v>
       </c>
       <c r="D37" t="n">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp6.450.000</t>
+          <t>Rp7.050.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>108</v>
       </c>
       <c r="D48" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp4.400.000</t>
+          <t>Rp4.950.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>98</v>
       </c>
       <c r="D49" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp8.420.000</t>
+          <t>Rp10.460.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>144</v>
       </c>
       <c r="D50" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp6.000.000</t>
+          <t>Rp6.175.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>76</v>
       </c>
       <c r="D2" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp2.655.000</t>
+          <t>Rp3.475.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8064,16 +8064,16 @@
         <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.240.000</t>
+          <t>Rp2.760.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -8095,16 +8095,16 @@
         <v>86</v>
       </c>
       <c r="D5" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp5.500.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp5.382.000</t>
+          <t>Rp5.681.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>51</v>
       </c>
       <c r="D7" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp3.885.000</t>
+          <t>Rp4.120.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.110.000</t>
+          <t>Rp4.515.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp4.060.000</t>
+          <t>Rp4.720.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp7.050.000</t>
+          <t>Rp7.320.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.050.000</t>
+          <t>Rp1.175.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.374.990</t>
+          <t>Rp4.274.988</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.825.000</t>
+          <t>Rp3.025.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp5.085.000</t>
+          <t>Rp4.435.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp17.680.000</t>
+          <t>Rp18.160.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp5.145.000</t>
+          <t>Rp5.535.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>36</v>
       </c>
       <c r="D25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.201.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp3.724.992</t>
+          <t>Rp4.424.991</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp5.575.000</t>
+          <t>Rp6.145.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp4.000.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.550.000</t>
+          <t>Rp2.775.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D33" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.097.000</t>
+          <t>Rp3.787.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>34</v>
       </c>
       <c r="D34" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.095.000</t>
+          <t>Rp3.390.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>36</v>
       </c>
       <c r="D36" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.510.000</t>
+          <t>Rp3.810.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9242,16 +9242,16 @@
         <v>72</v>
       </c>
       <c r="D42" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.975.000</t>
+          <t>Rp3.975.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -9273,16 +9273,16 @@
         <v>68</v>
       </c>
       <c r="D43" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp2.236.000</t>
+          <t>Rp2.435.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-09.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-09.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp2.240.000</t>
+          <t>Rp2.340.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -606,16 +606,16 @@
         <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp2.900.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp7.930.000</t>
+          <t>Rp8.430.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.900.000</t>
+          <t>Rp2.150.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -947,16 +947,16 @@
         <v>85</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp4.140.000</t>
+          <t>Rp4.440.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>72</v>
       </c>
       <c r="D18" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.400.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.625.000</t>
+          <t>Rp2.875.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.220.000</t>
+          <t>Rp3.380.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>108</v>
       </c>
       <c r="D70" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp4.825.000</t>
+          <t>Rp5.175.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>90</v>
       </c>
       <c r="D73" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp3.450.000</t>
+          <t>Rp4.100.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2714,16 +2714,16 @@
         <v>96</v>
       </c>
       <c r="D74" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rp1.715.000</t>
+          <t>Rp675.000</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>108</v>
       </c>
       <c r="D78" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp3.775.000</t>
+          <t>Rp3.175.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2897,24 +2897,24 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D80" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp5.161.000</t>
+          <t>Rp5.360.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Rp99.000 - Rp199.000</t>
+          <t>Rp50.000 - Rp199.000</t>
         </is>
       </c>
     </row>
@@ -2931,16 +2931,16 @@
         <v>54</v>
       </c>
       <c r="D81" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp1.985.000</t>
+          <t>Rp2.383.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>36</v>
       </c>
       <c r="D86" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp1.160.000</t>
+          <t>Rp1.540.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3179,16 +3179,16 @@
         <v>90</v>
       </c>
       <c r="D89" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp3.420.000</t>
+          <t>Rp1.980.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3396,16 +3396,16 @@
         <v>112</v>
       </c>
       <c r="D96" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rp4.485.000</t>
+          <t>Rp4.725.000</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -4253,16 +4253,16 @@
         <v>60</v>
       </c>
       <c r="D25" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp2.010.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>180</v>
       </c>
       <c r="D28" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp20.245.000</t>
+          <t>Rp20.745.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -5214,16 +5214,16 @@
         <v>75</v>
       </c>
       <c r="D56" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp275.000</t>
+          <t>Rp408.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>90</v>
       </c>
       <c r="D64" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp11.500.000</t>
+          <t>Rp10.700.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5761,16 +5761,16 @@
         <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp840.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>272</v>
       </c>
       <c r="D8" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp32.000.000</t>
+          <t>Rp33.200.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp3.550.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.095.000</t>
+          <t>Rp2.790.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>90</v>
       </c>
       <c r="D9" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp9.324.000</t>
+          <t>Rp9.720.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp3.100.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp15.960.000</t>
+          <t>Rp16.510.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp4.176.000</t>
+          <t>Rp4.451.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp14.150.000</t>
+          <t>Rp14.300.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>67</v>
       </c>
       <c r="D35" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp4.156.000</t>
+          <t>Rp4.444.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7796,16 +7796,16 @@
         <v>36</v>
       </c>
       <c r="D47" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp7.100.000</t>
+          <t>Rp7.600.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>98</v>
       </c>
       <c r="D49" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp10.460.000</t>
+          <t>Rp9.780.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp4.435.000</t>
+          <t>Rp5.360.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp3.500.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D33" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.787.000</t>
+          <t>Rp4.132.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>34</v>
       </c>
       <c r="D34" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.390.000</t>
+          <t>Rp3.095.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>36</v>
       </c>
       <c r="D36" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.810.000</t>
+          <t>Rp4.110.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>51</v>
       </c>
       <c r="D38" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.770.000</t>
+          <t>Rp2.110.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-09.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-09.xlsx
@@ -544,16 +544,16 @@
         <v>168</v>
       </c>
       <c r="D4" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp18.230.000</t>
+          <t>Rp18.480.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>68</v>
       </c>
       <c r="D10" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp7.692.984</t>
+          <t>Rp7.354.984</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>54</v>
       </c>
       <c r="D30" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.880.000</t>
+          <t>Rp3.360.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.454.000</t>
+          <t>Rp2.552.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp4.980.000</t>
+          <t>Rp5.105.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1877,16 +1877,16 @@
         <v>54</v>
       </c>
       <c r="D47" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp1.220.000</t>
+          <t>Rp1.420.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>36</v>
       </c>
       <c r="D59" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp1.291.000</t>
+          <t>Rp1.390.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>68</v>
       </c>
       <c r="D62" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp2.880.000</t>
+          <t>Rp3.360.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>127</v>
       </c>
       <c r="D3" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp15.962.500</t>
+          <t>Rp16.247.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp6.400.000</t>
+          <t>Rp6.750.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -4253,16 +4253,16 @@
         <v>60</v>
       </c>
       <c r="D25" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.010.000</t>
+          <t>Rp2.560.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>90</v>
       </c>
       <c r="D64" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp10.700.000</t>
+          <t>Rp10.950.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp11.325.000</t>
+          <t>Rp11.155.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5792,16 +5792,16 @@
         <v>333</v>
       </c>
       <c r="D3" t="n">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp11.385.000</t>
+          <t>Rp12.540.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>108</v>
       </c>
       <c r="D5" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp10.550.000</t>
+          <t>Rp11.050.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>272</v>
       </c>
       <c r="D8" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp33.200.000</t>
+          <t>Rp34.400.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.900.000</t>
+          <t>Rp6.075.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>96</v>
       </c>
       <c r="D3" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp8.000.000</t>
+          <t>Rp8.240.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp337.000</t>
+          <t>Rp1.011.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp17.789.000</t>
+          <t>Rp18.262.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp22.500.000</t>
+          <t>Rp22.900.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp6.750.000</t>
+          <t>Rp7.000.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>187</v>
       </c>
       <c r="D34" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp14.300.000</t>
+          <t>Rp14.650.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>76</v>
       </c>
       <c r="D2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp3.475.000</t>
+          <t>Rp3.625.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>51</v>
       </c>
       <c r="D7" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp4.120.000</t>
+          <t>Rp4.570.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.640.000</t>
+          <t>Rp1.790.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.515.000</t>
+          <t>Rp4.965.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp7.320.000</t>
+          <t>Rp7.720.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.025.000</t>
+          <t>Rp3.225.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>54</v>
       </c>
       <c r="D28" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp4.650.000</t>
+          <t>Rp4.950.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -9180,16 +9180,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp5.555.000</t>
+          <t>Rp5.855.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
